--- a/output/Data and Chart Outputs/texas_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/texas_gas_monthly.xlsx
@@ -192,6 +192,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Texas gas demand including LNG feedgas: consumption by sector plus LNG (EIA history, forecast to Dec/28) (to Dec/28; forecast from Aug/26, lighter bars)</a:t>
             </a:r>
           </a:p>
@@ -2806,6 +2807,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Texas LNG feedgas: history and forecast, base and 6-month delay (to Dec/28; forecast from Aug/26, lighter bars)</a:t>
             </a:r>
           </a:p>
@@ -3018,6 +3020,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Texas natural gas consumption by sector (EIA; lease/plant and pipeline fuel withheld by EIA) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -3265,6 +3268,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Texas natural gas exports by route: pipeline to Mexico and LNG (EIA) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -3540,6 +3544,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Texas pipeline exports to Mexico by border crossing (EIA) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -3731,6 +3736,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Texas gas balance: dry production against consumption, exports and the residual (EIA) (to Jul/26)</a:t>
             </a:r>
           </a:p>
